--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:51</t>
+    <t xml:space="preserve">2026-09-10 01:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:01</t>
+    <t xml:space="preserve">2026-09-18 11:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:08</t>
+    <t xml:space="preserve">2026-09-23 14:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:31</t>
+    <t xml:space="preserve">2026-10-02 15:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:50</t>
+    <t xml:space="preserve">2026-10-05 15:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -996,7 +996,7 @@
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="28">
